--- a/data/trans_bre/P1403-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P1403-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,76</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1803,31%</t>
+          <t>20,97%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 1,34</t>
+          <t>-0,16; 1,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 0,0</t>
+          <t>-1,06; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 0,45</t>
+          <t>-1,34; 0,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 3,02</t>
+          <t>-2,08; 1,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,23</t>
+          <t>-1,16</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-19,93%</t>
+          <t>-56,05%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,43</t>
+          <t>0,38; 2,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 1,97</t>
+          <t>-0,68; 2,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 0,07</t>
+          <t>-2,27; -0,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 1,04</t>
+          <t>-3,51; 0,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-24,77; —</t>
+          <t>-17,61; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-56,56; 336,44</t>
+          <t>-52,18; 341,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 102,86</t>
+          <t>-100,0; 66,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-86,89; 298,24</t>
+          <t>-90,04; 89,96</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1,26</t>
+          <t>-1,46</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-34,14%</t>
+          <t>-38,57%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 3,44</t>
+          <t>-0,79; 3,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 0,93</t>
+          <t>-3,38; 0,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 0,83</t>
+          <t>-2,88; 0,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 0,59</t>
+          <t>-3,56; 0,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-19,31; 150,56</t>
+          <t>-19,43; 165,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-57,7; 29,16</t>
+          <t>-58,2; 28,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-64,59; 37,02</t>
+          <t>-62,35; 35,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-64,91; 26,19</t>
+          <t>-67,63; 18,33</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,67</t>
+          <t>-3,32</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>-20,72%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 0,82</t>
+          <t>-7,17; 1,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 5,27</t>
+          <t>-2,44; 5,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,2; -0,82</t>
+          <t>-7,99; -0,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 9,7</t>
+          <t>-6,76; 0,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-43,24; 6,93</t>
+          <t>-44,04; 9,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-19,78; 53,49</t>
+          <t>-17,38; 58,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-53,03; -5,84</t>
+          <t>-51,75; -7,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-29,91; 147,31</t>
+          <t>-37,55; 2,16</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-3,27</t>
+          <t>-1,86</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-11,05%</t>
+          <t>-6,5%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 7,02</t>
+          <t>-5,49; 7,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 10,93</t>
+          <t>-2,95; 10,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 10,01</t>
+          <t>-1,4; 10,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 1,35</t>
+          <t>-6,43; 2,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-17,14; 24,99</t>
+          <t>-16,3; 25,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 34,79</t>
+          <t>-7,41; 32,82</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,84; 43,29</t>
+          <t>-4,73; 47,37</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-24,81; 5,36</t>
+          <t>-20,16; 8,8</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18,08</t>
+          <t>1,28</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 14,43</t>
+          <t>-0,55; 14,72</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 14,05</t>
+          <t>-2,59; 13,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 13,1</t>
+          <t>-2,14; 12,82</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 42,83</t>
+          <t>-3,97; 7,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 40,52</t>
+          <t>-1,53; 42,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 29,69</t>
+          <t>-4,94; 27,75</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 35,87</t>
+          <t>-4,78; 34,82</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 99,23</t>
+          <t>-8,02; 18,3</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10,13</t>
+          <t>10,09</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,65%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 17,81</t>
+          <t>0,56; 18,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 13,01</t>
+          <t>-2,86; 13,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 11,11</t>
+          <t>-5,22; 11,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,63; 15,91</t>
+          <t>4,26; 16,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 41,67</t>
+          <t>1,05; 44,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 24,18</t>
+          <t>-4,43; 25,29</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,05; 22,14</t>
+          <t>-9,17; 22,94</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,31; 31,5</t>
+          <t>7,44; 33,09</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7,19</t>
+          <t>1,8</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>9,4%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,28; 5,75</t>
+          <t>2,31; 5,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,13; 5,92</t>
+          <t>2,13; 5,98</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,89; 4,33</t>
+          <t>0,75; 4,46</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,88; 22,99</t>
+          <t>0,08; 3,48</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>16,76; 48,07</t>
+          <t>16,24; 47,11</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,86; 36,81</t>
+          <t>11,78; 37,9</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,45; 30,04</t>
+          <t>4,7; 30,79</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>10,2; 139,52</t>
+          <t>0,36; 19,05</t>
         </is>
       </c>
     </row>
